--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132738507</v>
+        <v>132738508</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629787</v>
+        <v>629802</v>
       </c>
       <c r="R2" t="n">
-        <v>6904888</v>
+        <v>6904903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738508</v>
+        <v>132738493</v>
       </c>
       <c r="B3" t="n">
         <v>79359</v>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629802</v>
+        <v>629679</v>
       </c>
       <c r="R3" t="n">
-        <v>6904903</v>
+        <v>6904752</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738493</v>
+        <v>132738507</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +885,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629679</v>
+        <v>629787</v>
       </c>
       <c r="R4" t="n">
-        <v>6904752</v>
+        <v>6904888</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd på flera träd i närområdet</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B10" t="n">
-        <v>92333</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R10" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>92333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R11" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738512</v>
+        <v>132738501</v>
       </c>
       <c r="B13" t="n">
-        <v>99117</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629609</v>
+        <v>629712</v>
       </c>
       <c r="R13" t="n">
-        <v>6904903</v>
+        <v>6904785</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1841,6 +1841,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738501</v>
+        <v>132738512</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629712</v>
+        <v>629609</v>
       </c>
       <c r="R14" t="n">
-        <v>6904785</v>
+        <v>6904903</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1938,11 +1943,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738506</v>
+        <v>132738504</v>
       </c>
       <c r="B17" t="n">
-        <v>99117</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629751</v>
+        <v>629668</v>
       </c>
       <c r="R17" t="n">
-        <v>6904881</v>
+        <v>6904752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,32 +2372,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132738504</v>
+        <v>132738506</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629668</v>
+        <v>629751</v>
       </c>
       <c r="R19" t="n">
-        <v>6904752</v>
+        <v>6904881</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
         <v>132738509</v>
       </c>
       <c r="B21" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132738508</v>
+        <v>132738507</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629802</v>
+        <v>629787</v>
       </c>
       <c r="R2" t="n">
-        <v>6904903</v>
+        <v>6904888</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738493</v>
+        <v>132738508</v>
       </c>
       <c r="B3" t="n">
         <v>79359</v>
@@ -807,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629679</v>
+        <v>629802</v>
       </c>
       <c r="R3" t="n">
-        <v>6904752</v>
+        <v>6904903</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738507</v>
+        <v>132738493</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629787</v>
+        <v>629679</v>
       </c>
       <c r="R4" t="n">
-        <v>6904888</v>
+        <v>6904752</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132738491</v>
+        <v>132738497</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629704</v>
+        <v>629755</v>
       </c>
       <c r="R7" t="n">
-        <v>6904751</v>
+        <v>6904768</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132738497</v>
+        <v>132738491</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629755</v>
+        <v>629704</v>
       </c>
       <c r="R8" t="n">
-        <v>6904768</v>
+        <v>6904751</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>92333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R10" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B11" t="n">
-        <v>92333</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R11" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2270,53 +2270,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738495</v>
+        <v>132738506</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629647</v>
+        <v>629751</v>
       </c>
       <c r="R18" t="n">
-        <v>6904772</v>
+        <v>6904881</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2372,48 +2367,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132738506</v>
+        <v>132738495</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629751</v>
+        <v>629647</v>
       </c>
       <c r="R19" t="n">
-        <v>6904881</v>
+        <v>6904772</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132738507</v>
+        <v>132738508</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629787</v>
+        <v>629802</v>
       </c>
       <c r="R2" t="n">
-        <v>6904888</v>
+        <v>6904903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738508</v>
+        <v>132738493</v>
       </c>
       <c r="B3" t="n">
         <v>79359</v>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629802</v>
+        <v>629679</v>
       </c>
       <c r="R3" t="n">
-        <v>6904903</v>
+        <v>6904752</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738493</v>
+        <v>132738507</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +885,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629679</v>
+        <v>629787</v>
       </c>
       <c r="R4" t="n">
-        <v>6904752</v>
+        <v>6904888</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd på flera träd i närområdet</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738504</v>
+        <v>132738506</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629668</v>
+        <v>629751</v>
       </c>
       <c r="R17" t="n">
-        <v>6904752</v>
+        <v>6904881</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2270,32 +2270,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738506</v>
+        <v>132738504</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629751</v>
+        <v>629668</v>
       </c>
       <c r="R18" t="n">
-        <v>6904881</v>
+        <v>6904752</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2469,53 +2469,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R20" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2571,48 +2566,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R21" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132738508</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132738493</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132738507</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>132738498</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>132738492</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132738497</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132738491</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>132738494</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B10" t="n">
-        <v>92333</v>
+        <v>91910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R10" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>92334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R11" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>132738502</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738501</v>
+        <v>132738512</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629712</v>
+        <v>629609</v>
       </c>
       <c r="R13" t="n">
-        <v>6904785</v>
+        <v>6904903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1841,11 +1841,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1872,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738512</v>
+        <v>132738501</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>79328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629609</v>
+        <v>629712</v>
       </c>
       <c r="R14" t="n">
-        <v>6904903</v>
+        <v>6904785</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1943,6 +1938,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1972,7 +1972,7 @@
         <v>132738511</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>132738510</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738506</v>
+        <v>132738504</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629751</v>
+        <v>629668</v>
       </c>
       <c r="R17" t="n">
-        <v>6904881</v>
+        <v>6904752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738504</v>
+        <v>132738495</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>57954</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2281,37 +2281,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629668</v>
+        <v>629647</v>
       </c>
       <c r="R18" t="n">
-        <v>6904752</v>
+        <v>6904772</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2367,53 +2372,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132738495</v>
+        <v>132738506</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>99119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629647</v>
+        <v>629751</v>
       </c>
       <c r="R19" t="n">
-        <v>6904772</v>
+        <v>6904881</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2469,48 +2469,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>57954</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R20" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2566,53 +2571,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>99119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R21" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>132738496</v>
       </c>
       <c r="B22" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132738507</v>
+        <v>132738508</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629787</v>
+        <v>629802</v>
       </c>
       <c r="R2" t="n">
-        <v>6904888</v>
+        <v>6904903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738508</v>
+        <v>132738493</v>
       </c>
       <c r="B3" t="n">
         <v>79365</v>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629802</v>
+        <v>629679</v>
       </c>
       <c r="R3" t="n">
-        <v>6904903</v>
+        <v>6904752</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738493</v>
+        <v>132738507</v>
       </c>
       <c r="B4" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +885,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629679</v>
+        <v>629787</v>
       </c>
       <c r="R4" t="n">
-        <v>6904752</v>
+        <v>6904888</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd på flera träd i närområdet</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>92342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R10" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B11" t="n">
-        <v>92342</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R11" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2469,48 +2469,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R20" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2566,53 +2571,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R21" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B10" t="n">
-        <v>92342</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R10" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>92342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R11" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738504</v>
+        <v>132738495</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,37 +2184,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629668</v>
+        <v>629647</v>
       </c>
       <c r="R17" t="n">
-        <v>6904752</v>
+        <v>6904772</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2270,10 +2275,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738495</v>
+        <v>132738504</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2281,42 +2286,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629647</v>
+        <v>629668</v>
       </c>
       <c r="R18" t="n">
-        <v>6904772</v>
+        <v>6904752</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2469,53 +2469,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R20" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2571,48 +2566,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R21" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -2173,10 +2173,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738495</v>
+        <v>132738504</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,42 +2184,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629647</v>
+        <v>629668</v>
       </c>
       <c r="R17" t="n">
-        <v>6904772</v>
+        <v>6904752</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738504</v>
+        <v>132738495</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2286,37 +2281,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629668</v>
+        <v>629647</v>
       </c>
       <c r="R18" t="n">
-        <v>6904752</v>
+        <v>6904772</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2469,48 +2469,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R20" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2566,53 +2571,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R21" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738493</v>
+        <v>132738507</v>
       </c>
       <c r="B3" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629679</v>
+        <v>629787</v>
       </c>
       <c r="R3" t="n">
-        <v>6904752</v>
+        <v>6904888</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd på flera träd i närområdet</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738507</v>
+        <v>132738493</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629787</v>
+        <v>629679</v>
       </c>
       <c r="R4" t="n">
-        <v>6904888</v>
+        <v>6904752</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132738491</v>
+        <v>132738497</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629704</v>
+        <v>629755</v>
       </c>
       <c r="R7" t="n">
-        <v>6904751</v>
+        <v>6904768</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132738497</v>
+        <v>132738491</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629755</v>
+        <v>629704</v>
       </c>
       <c r="R8" t="n">
-        <v>6904768</v>
+        <v>6904751</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>92342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R10" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B11" t="n">
-        <v>92342</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R11" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738501</v>
+        <v>132738512</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629712</v>
+        <v>629609</v>
       </c>
       <c r="R13" t="n">
-        <v>6904785</v>
+        <v>6904903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1841,11 +1841,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1872,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738512</v>
+        <v>132738501</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629609</v>
+        <v>629712</v>
       </c>
       <c r="R14" t="n">
-        <v>6904903</v>
+        <v>6904785</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1943,6 +1938,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2270,53 +2270,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738495</v>
+        <v>132738506</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629647</v>
+        <v>629751</v>
       </c>
       <c r="R18" t="n">
-        <v>6904772</v>
+        <v>6904881</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2372,48 +2367,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132738506</v>
+        <v>132738495</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629751</v>
+        <v>629647</v>
       </c>
       <c r="R19" t="n">
-        <v>6904881</v>
+        <v>6904772</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738507</v>
+        <v>132738493</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629787</v>
+        <v>629679</v>
       </c>
       <c r="R3" t="n">
-        <v>6904888</v>
+        <v>6904752</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738493</v>
+        <v>132738507</v>
       </c>
       <c r="B4" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +885,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629679</v>
+        <v>629787</v>
       </c>
       <c r="R4" t="n">
-        <v>6904752</v>
+        <v>6904888</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spridd på flera träd i närområdet</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738500</v>
+        <v>132738490</v>
       </c>
       <c r="B10" t="n">
-        <v>92342</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629721</v>
+        <v>629703</v>
       </c>
       <c r="R10" t="n">
-        <v>6904767</v>
+        <v>6904728</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738490</v>
+        <v>132738500</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>92342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629703</v>
+        <v>629721</v>
       </c>
       <c r="R11" t="n">
-        <v>6904728</v>
+        <v>6904767</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738512</v>
+        <v>132738501</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629609</v>
+        <v>629712</v>
       </c>
       <c r="R13" t="n">
-        <v>6904903</v>
+        <v>6904785</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1841,6 +1841,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738501</v>
+        <v>132738512</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629712</v>
+        <v>629609</v>
       </c>
       <c r="R14" t="n">
-        <v>6904785</v>
+        <v>6904903</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1938,11 +1943,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132738497</v>
+        <v>132738491</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629755</v>
+        <v>629704</v>
       </c>
       <c r="R7" t="n">
-        <v>6904768</v>
+        <v>6904751</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132738491</v>
+        <v>132738497</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629704</v>
+        <v>629755</v>
       </c>
       <c r="R8" t="n">
-        <v>6904751</v>
+        <v>6904768</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1770,32 +1770,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738501</v>
+        <v>132738512</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629712</v>
+        <v>629609</v>
       </c>
       <c r="R13" t="n">
-        <v>6904785</v>
+        <v>6904903</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1841,11 +1841,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1872,32 +1867,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738512</v>
+        <v>132738501</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629609</v>
+        <v>629712</v>
       </c>
       <c r="R14" t="n">
-        <v>6904903</v>
+        <v>6904785</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1943,6 +1938,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2469,53 +2469,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R20" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2571,48 +2566,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R21" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132738491</v>
+        <v>132738497</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629704</v>
+        <v>629755</v>
       </c>
       <c r="R7" t="n">
-        <v>6904751</v>
+        <v>6904768</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132738497</v>
+        <v>132738491</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629755</v>
+        <v>629704</v>
       </c>
       <c r="R8" t="n">
-        <v>6904768</v>
+        <v>6904751</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -2469,48 +2469,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738509</v>
+        <v>132738499</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629761</v>
+        <v>629734</v>
       </c>
       <c r="R20" t="n">
-        <v>6904947</v>
+        <v>6904761</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2566,53 +2571,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738499</v>
+        <v>132738509</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629734</v>
+        <v>629761</v>
       </c>
       <c r="R21" t="n">
-        <v>6904761</v>
+        <v>6904947</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132738508</v>
+        <v>132738493</v>
       </c>
       <c r="B2" t="n">
-        <v>79365</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629802</v>
+        <v>629679</v>
       </c>
       <c r="R2" t="n">
-        <v>6904903</v>
+        <v>6904752</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132738493</v>
+        <v>132738508</v>
       </c>
       <c r="B3" t="n">
-        <v>79365</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629679</v>
+        <v>629802</v>
       </c>
       <c r="R3" t="n">
-        <v>6904752</v>
+        <v>6904903</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spridd på flera träd i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132738507</v>
+        <v>132738490</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,42 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629787</v>
+        <v>629703</v>
       </c>
       <c r="R4" t="n">
-        <v>6904888</v>
+        <v>6904728</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -950,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132738498</v>
+        <v>132738491</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,42 +982,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629750</v>
+        <v>629704</v>
       </c>
       <c r="R5" t="n">
-        <v>6904756</v>
+        <v>6904751</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132738492</v>
+        <v>132738494</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629687</v>
+        <v>629652</v>
       </c>
       <c r="R6" t="n">
-        <v>6904738</v>
+        <v>6904772</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132738497</v>
+        <v>132738496</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629755</v>
+        <v>629757</v>
       </c>
       <c r="R7" t="n">
-        <v>6904768</v>
+        <v>6904766</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132738491</v>
+        <v>132738504</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629704</v>
+        <v>629668</v>
       </c>
       <c r="R8" t="n">
-        <v>6904751</v>
+        <v>6904752</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132738494</v>
+        <v>132738500</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>92370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629652</v>
+        <v>629721</v>
       </c>
       <c r="R9" t="n">
-        <v>6904772</v>
+        <v>6904767</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1471,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132738490</v>
+        <v>132738492</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629703</v>
+        <v>629687</v>
       </c>
       <c r="R10" t="n">
-        <v>6904728</v>
+        <v>6904738</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132738500</v>
+        <v>132738497</v>
       </c>
       <c r="B11" t="n">
-        <v>92342</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629721</v>
+        <v>629755</v>
       </c>
       <c r="R11" t="n">
-        <v>6904767</v>
+        <v>6904768</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1665,56 +1650,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132738502</v>
+        <v>132738501</v>
       </c>
       <c r="B12" t="n">
-        <v>58119</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629718</v>
+        <v>629712</v>
       </c>
       <c r="R12" t="n">
-        <v>6904879</v>
+        <v>6904785</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1744,6 +1721,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132738512</v>
+        <v>132738505</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629609</v>
+        <v>629797</v>
       </c>
       <c r="R13" t="n">
-        <v>6904903</v>
+        <v>6904830</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,14 +1849,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132738501</v>
+        <v>132738510</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1902,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629712</v>
+        <v>629640</v>
       </c>
       <c r="R14" t="n">
-        <v>6904785</v>
+        <v>6904880</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1938,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1969,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132738511</v>
+        <v>132738495</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,7 +1977,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2009,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>629642</v>
+        <v>629647</v>
       </c>
       <c r="R15" t="n">
-        <v>6904917</v>
+        <v>6904772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132738510</v>
+        <v>132738498</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2087,37 +2059,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629640</v>
+        <v>629750</v>
       </c>
       <c r="R16" t="n">
-        <v>6904880</v>
+        <v>6904756</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132738504</v>
+        <v>132738499</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2184,37 +2161,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629668</v>
+        <v>629734</v>
       </c>
       <c r="R17" t="n">
-        <v>6904752</v>
+        <v>6904761</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2270,48 +2252,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132738506</v>
+        <v>132738507</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629751</v>
+        <v>629787</v>
       </c>
       <c r="R18" t="n">
-        <v>6904881</v>
+        <v>6904888</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2341,6 +2328,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2367,10 +2359,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132738495</v>
+        <v>132738511</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2390,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2407,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629647</v>
+        <v>629642</v>
       </c>
       <c r="R19" t="n">
-        <v>6904772</v>
+        <v>6904917</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,6 +2435,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2469,10 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132738499</v>
+        <v>132738502</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2480,42 +2477,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629734</v>
+        <v>629718</v>
       </c>
       <c r="R20" t="n">
-        <v>6904761</v>
+        <v>6904879</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2571,48 +2571,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132738509</v>
+        <v>132738503</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>58131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ässjötjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629761</v>
+        <v>629676</v>
       </c>
       <c r="R21" t="n">
-        <v>6904947</v>
+        <v>6904747</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2668,32 +2673,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132738496</v>
+        <v>132738506</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629757</v>
+        <v>629751</v>
       </c>
       <c r="R22" t="n">
-        <v>6904766</v>
+        <v>6904881</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2762,6 +2767,200 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132738509</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ässjötjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629761</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6904947</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132738512</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ässjötjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629609</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6904903</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15540-2026 artfynd.xlsx
+++ b/artfynd/A 15540-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738508</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738490</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738491</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738494</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738496</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738504</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738497</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738501</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738505</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738498</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738499</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738507</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738502</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2670,6 +2770,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738503</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2767,6 +2872,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2864,6 +2974,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738509</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2961,8 +3076,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>